--- a/docs/3.Managing_Data_for_Generative_AI.xlsx
+++ b/docs/3.Managing_Data_for_Generative_AI.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\study\Ultimate_AWS_Certified_Generative_AI_Developer_Professional\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EAF2D2-402C-4DB8-8BD0-C933EFA09A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DB1B44-A105-4C04-A1BE-459F52CA2D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Amazon Bedrock Data Automation" sheetId="1" r:id="rId1"/>
+    <sheet name="DemoSageMakerStudioCanvas&amp;Data" sheetId="2" r:id="rId2"/>
+    <sheet name="AWS Glue Studio" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <r>
       <t>có demo s</t>
@@ -1319,6 +1321,514 @@
         <scheme val="minor"/>
       </rPr>
       <t>nh, video, audio</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Demo: SageMaker Studio, Canvas, and Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ầ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t domain đ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> có th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ử</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ụ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ng Studio. Vì v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ậ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>y đây ch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ỉ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t cách đ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> xem ai đư</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ợ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>c phép làm gì.</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ấ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>y danh sách các ngu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ồ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ữ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u đã tăng lên đáng k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> theo th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ờ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i gian</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>thêm m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t node cho ngu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ồ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ữ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>click vào node ngu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ồ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ữ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -1818,6 +2328,412 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>86088</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4CF0B18-37F0-CB9D-EA3F-72F2E6851F19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="742950" y="762000"/>
+          <a:ext cx="14830425" cy="7102838"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>72571</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>412750</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>16184</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B0131E3-332E-2D38-3BBC-CE756E5531AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="739321" y="8554358"/>
+          <a:ext cx="15008679" cy="5908076"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>90715</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>90716</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>204198</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88D91340-1A08-3EDA-8EB9-AEA48676F2DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="757465" y="14759216"/>
+          <a:ext cx="14958786" cy="6114232"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>125133</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>162485</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>426758</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>76814</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AE75510-90B6-7272-C0A2-48573CF23C90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="782545" y="394073"/>
+          <a:ext cx="14764684" cy="7788329"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>59765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>460375</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>102788</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B03DB467-51C5-523B-0E2B-9885E51F4713}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="793750" y="8060765"/>
+          <a:ext cx="15001875" cy="7377273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>194235</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>67236</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>34851</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51726533-2B88-DE15-DEFE-5F0DE825740C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="860985" y="15624736"/>
+          <a:ext cx="14855265" cy="7301865"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>145143</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>117928</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>75242</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E54BC405-2374-D633-D4E5-56AA9055ABC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="811893" y="23454178"/>
+          <a:ext cx="14872607" cy="7513814"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>127001</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>97117</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>473365</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>140988</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A0D6C9E-A1CB-FDEC-FE26-1CF1F124CBE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="785092" y="32886208"/>
+          <a:ext cx="14824364" cy="7663871"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>392545</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>46546</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C76E8D0F-D711-EF3C-A4D9-598C1B74A999}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="785091" y="40991559"/>
+          <a:ext cx="14743545" cy="7776805"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2146,4 +3062,54 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024D6694-A0A7-4FE8-99AF-C2BBD5445139}">
+  <dimension ref="B2:B38"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E792E072-4CE3-46E3-92A5-27420F8550E2}">
+  <dimension ref="B105:B177"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="105" spans="2:2">
+      <c r="B105" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>